--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441426</v>
+        <v>113441461</v>
       </c>
       <c r="B2" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>786113</v>
+        <v>786080</v>
       </c>
       <c r="R2" t="n">
-        <v>7216801</v>
+        <v>7216837</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441461</v>
+        <v>113441426</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>786080</v>
+        <v>786113</v>
       </c>
       <c r="R3" t="n">
-        <v>7216837</v>
+        <v>7216801</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441461</v>
+        <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>786080</v>
+        <v>786309</v>
       </c>
       <c r="R2" t="n">
-        <v>7216837</v>
+        <v>7217165</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,57 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441426</v>
+        <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>57144</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>786113</v>
+        <v>786256</v>
       </c>
       <c r="R3" t="n">
-        <v>7216801</v>
+        <v>7217118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,15 +877,918 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113441461</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>786080</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7216837</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Tobias Pettersson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Tobias Pettersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134650462</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>786092</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7216833</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134650464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>786099</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7216832</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska barksprätt bild</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134650470</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>786131</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7216737</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134650481</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>786312</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7217262</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134650483</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>786263</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7217156</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En adult och ett gäng kycklingar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113441426</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>786113</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7216801</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134650466</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>786134</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7216790</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650485</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441461</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650462</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650481</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,6 +1620,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650483</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1682,6 +1727,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441426</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1789,8 +1839,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650466</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113441461</v>
+        <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>92048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>786080</v>
+        <v>786309</v>
       </c>
       <c r="R2" t="n">
-        <v>7216837</v>
+        <v>7217165</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,62 +775,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tobias Pettersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113441461</t>
+          <t>https://artportalen.se/Sighting/134650479</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113441426</v>
+        <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>57144</v>
+        <v>92048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västerbottens län, Vb</t>
+          <t>Nördrengårdsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>786113</v>
+        <v>786256</v>
       </c>
       <c r="R3" t="n">
-        <v>7216801</v>
+        <v>7217118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sweco NVI</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,18 +891,989 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650485</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113441461</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>786080</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7216837</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Tobias Pettersson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Tobias Pettersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113441461</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134650462</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>786092</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7216833</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650462</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134650464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>786099</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7216832</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska barksprätt bild</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650464</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134650470</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>786131</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7216737</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650470</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134650481</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>786312</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7217262</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650481</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134650483</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57158</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>786263</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7217156</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En adult och ett gäng kycklingar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650483</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113441426</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västerbottens län, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>786113</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7216801</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sweco NVI</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113441426</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134650466</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nördrengårdsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>786134</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7216790</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134650466</t>
         </is>
       </c>
     </row>
@@ -896,6 +1881,14 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>134650462</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>134650464</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>134650470</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>134650481</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>134650483</v>
       </c>
       <c r="B9" t="n">
-        <v>57158</v>
+        <v>57160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>134650466</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>134650462</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>134650464</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>134650470</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>134650481</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>134650483</v>
       </c>
       <c r="B9" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>134650462</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>134650464</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>134650470</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>134650481</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>134650483</v>
       </c>
       <c r="B9" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>134650462</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>134650464</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>134650470</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>134650481</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>134650483</v>
       </c>
       <c r="B9" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>134650462</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>134650464</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>134650470</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>134650481</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>134650483</v>
       </c>
       <c r="B9" t="n">
-        <v>57166</v>
+        <v>57171</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26646-2026 artfynd.xlsx
+++ b/artfynd/A 26646-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134650479</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134650485</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
